--- a/assets/r34_en/sheets/characters.xlsx
+++ b/assets/r34_en/sheets/characters.xlsx
@@ -419,12 +419,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>名稱</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>職業</t>
+          <t>Class</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -434,24 +434,24 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>備註</t>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>阿傑</t>
+          <t>A-Jie</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>地師</t>
+          <t>Earth Master</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -459,24 +459,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>分金定穴</t>
+          <t>Vein Pinpointing</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>民國初年生人</t>
+          <t>Born in the early Republican era</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>小滿</t>
+          <t>Xiao-Man</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>符籙弟子</t>
+          <t>Talisman Apprentice</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -484,12 +484,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>符咒</t>
+          <t>Talisman</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>膽子小但手穩</t>
+          <t>Timid but steady-handed</t>
         </is>
       </c>
     </row>
